--- a/files/Life_Insurance_KPI_Dashboard.xlsx
+++ b/files/Life_Insurance_KPI_Dashboard.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,25 +26,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00707070"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00707070"/>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,10 +59,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,20 +77,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D7E2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7E2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,14 +483,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -464,112 +506,632 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Filename: Life_Insurance_KPI_Dashboard.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Source file: Life_Insurance_KPI_Dashboard.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>KPI</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>FY2026 Plan</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>vs Target</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>RAG</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Revenue (MYR M)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1820</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2150</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2480</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Placeholder figures</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Group revenue</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>MYR B</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>↑ improving</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EBITDA (MYR M)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>312</v>
-      </c>
-      <c r="C6" t="n">
-        <v>378</v>
-      </c>
-      <c r="D6" t="n">
-        <v>435</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Placeholder figures</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Group EBITDA</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>MYR B</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>→ flat</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Amber</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Net Margin (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Placeholder figures</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>↓ slipping</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>MYR B</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>↓ slipping</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Placeholder file used by the Zava Conglomerate Copilot Demo Hub. Replace with the actual workbook before live use.</t>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>↓ slipping</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Return on capital</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>↑ improving</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Customer NPS</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>46.23</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>↑ improving</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Employee engagement</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>83.79000000000001</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>↓ slipping</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Top-talent retention</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>96.62</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>↓ slipping</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Cost-to-income</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>↑ improving</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Scope 1+2 emissions</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>kt CO2e</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>412</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>437.89</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>↓ slipping</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Daichi Maruyama</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Lost-time injury rate</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>per M hrs</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>→ flat</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Cyber incidents (Sev1+2)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>→ flat</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Days sales outstanding</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>53.06</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>↓ slipping</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Capex utilisation</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>92.81999999999999</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>→ flat</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Strategic-initiative on-track</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>72.81</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>↑ improving</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
